--- a/artfynd/A 33191-2022 artfynd.xlsx
+++ b/artfynd/A 33191-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33191-2022 artfynd.xlsx
+++ b/artfynd/A 33191-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2060,6 +2060,109 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>111827327</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91876</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Färgelanda, Dls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>335014</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6509689</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Färgelanda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Järbo</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Samuel Sjöberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Samuel Sjöberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33191-2022 artfynd.xlsx
+++ b/artfynd/A 33191-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103382698</v>
+        <v>104306126</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96092</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>782</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stora Mölntjärnet, Dls</t>
+          <t>Färgelanda, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334963.7987556658</v>
+        <v>334977</v>
       </c>
       <c r="R2" t="n">
-        <v>6509916.733230451</v>
+        <v>6509733</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,70 +755,67 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Christine Bryngelsson, Jenny Larsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104945556</v>
+        <v>104306813</v>
       </c>
       <c r="B3" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96092</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>782</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Färgelanda, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>335111.950243502</v>
+        <v>335025</v>
       </c>
       <c r="R3" t="n">
-        <v>6509747.576712221</v>
+        <v>6509651</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -863,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-12-05</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-12-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,69 +856,68 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Samuel Sjöberg</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Samuel Sjöberg</t>
+          <t>Christine Bryngelsson, Jenny Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104945554</v>
+        <v>104307635</v>
       </c>
       <c r="B4" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96092</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>230185</v>
+        <v>782</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Färgelanda, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334999.6889441147</v>
+        <v>335017</v>
       </c>
       <c r="R4" t="n">
-        <v>6509669.611706472</v>
+        <v>6509697</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -976,22 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-12-05</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-12-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,55 +958,51 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Samuel Sjöberg</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Samuel Sjöberg</t>
+          <t>Christine Bryngelsson, Jenny Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104945559</v>
+        <v>104929994</v>
       </c>
       <c r="B5" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96092</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>782</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>335013.558577885</v>
+        <v>334932</v>
       </c>
       <c r="R5" t="n">
-        <v>6509689.31578509</v>
+        <v>6509728</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1092,19 +1046,9 @@
           <t>2022-12-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-12-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,63 +1063,58 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Samuel Sjöberg</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Samuel Sjöberg</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104928561</v>
+        <v>108668387</v>
       </c>
       <c r="B6" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96092</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>230185</v>
+        <v>782</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Färgelanda, Dls</t>
+          <t>Loften, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>334992.7256770025</v>
+        <v>334987</v>
       </c>
       <c r="R6" t="n">
-        <v>6509665.224504987</v>
+        <v>6509654</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1202,22 +1141,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-12-05</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-12-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,37 +1173,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104929821</v>
+        <v>111826663</v>
       </c>
       <c r="B7" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>788</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1287,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>335015.8861269953</v>
+        <v>334977</v>
       </c>
       <c r="R7" t="n">
-        <v>6509670.484450486</v>
+        <v>6509733</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1317,22 +1241,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-12-05</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-12-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,44 +1267,39 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson</t>
+          <t>Christine Bryngelsson, Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104929994</v>
+        <v>111826671</v>
       </c>
       <c r="B8" t="n">
-        <v>92805</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1401,10 +1310,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>334932.3464563376</v>
+        <v>335014</v>
       </c>
       <c r="R8" t="n">
-        <v>6509728.671249012</v>
+        <v>6509689</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1431,22 +1340,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-12-05</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-12-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,65 +1360,58 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson</t>
+          <t>Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson</t>
+          <t>Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104929808</v>
+        <v>111827327</v>
       </c>
       <c r="B9" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>4368</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Färgelanda, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>335023.7890410337</v>
+        <v>335014</v>
       </c>
       <c r="R9" t="n">
-        <v>6509684.718315544</v>
+        <v>6509689</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1546,22 +1438,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-12-05</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-12-05</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1570,54 +1452,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson</t>
+          <t>Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson</t>
+          <t>Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104306126</v>
+        <v>104930142</v>
       </c>
       <c r="B10" t="n">
-        <v>92805</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,21 +1481,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>782</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1650,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>334977.3169877924</v>
+        <v>334908</v>
       </c>
       <c r="R10" t="n">
-        <v>6509731.962975406</v>
+        <v>6509601</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1680,22 +1536,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-10-25</t>
+          <t>2022-12-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-10-25</t>
+          <t>2022-12-05</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,66 +1566,58 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson</t>
+          <t>Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson, Jenny Larsson</t>
+          <t>Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104307635</v>
+        <v>108668733</v>
       </c>
       <c r="B11" t="n">
-        <v>92805</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>107609</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>782</v>
+        <v>219686</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Färgelanda, Dls</t>
+          <t>Loften, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>335017.5100291509</v>
+        <v>335013</v>
       </c>
       <c r="R11" t="n">
-        <v>6509696.432684973</v>
+        <v>6509585</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1796,22 +1644,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-10-25</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-10-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,7 +1658,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1832,44 +1669,39 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson, Jenny Larsson</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104306813</v>
+        <v>103382698</v>
       </c>
       <c r="B12" t="n">
-        <v>92805</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>782</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1879,17 +1711,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Färgelanda, Dls</t>
+          <t>Stora Mölntjärnet, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>335025.0004044323</v>
+        <v>334964</v>
       </c>
       <c r="R12" t="n">
-        <v>6509651.885003244</v>
+        <v>6509917</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1913,22 +1745,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-10-25</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-10-25</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,65 +1766,58 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson, Jenny Larsson</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111826663</v>
+        <v>108668744</v>
       </c>
       <c r="B13" t="n">
-        <v>90817</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>788</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Färgelanda, Dls</t>
+          <t>Loften, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>334977</v>
+        <v>335013</v>
       </c>
       <c r="R13" t="n">
-        <v>6509732</v>
+        <v>6509585</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2029,12 +1844,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2043,7 +1858,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2055,58 +1869,55 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson, Samuel Sjöberg</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111827327</v>
+        <v>104929808</v>
       </c>
       <c r="B14" t="n">
-        <v>91973</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4368</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Färgelanda, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>335014</v>
+        <v>335024</v>
       </c>
       <c r="R14" t="n">
-        <v>6509689</v>
+        <v>6509685</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2133,12 +1944,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2022-12-05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2022-12-05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2147,69 +1958,87 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Samuel Sjöberg</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Samuel Sjöberg</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111826671</v>
+        <v>104929821</v>
       </c>
       <c r="B15" t="n">
-        <v>91957</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>788</v>
+        <v>229497</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Färgelanda, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>335014</v>
+        <v>335015</v>
       </c>
       <c r="R15" t="n">
-        <v>6509689</v>
+        <v>6509671</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2236,12 +2065,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2022-12-05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2022-12-05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2250,21 +2079,414 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
+          <t>Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>104945556</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Färgelanda, Dls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>335112</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6509748</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Färgelanda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Järbo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-12-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-12-05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>Samuel Sjöberg</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>Samuel Sjöberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>104945559</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Färgelanda, Dls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>335014</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6509689</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Färgelanda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Järbo</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-12-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-12-05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Samuel Sjöberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Samuel Sjöberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>104928561</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Färgelanda, Dls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>334993</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6509665</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Färgelanda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Järbo</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-12-05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-12-05</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>104945554</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Färgelanda, Dls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>335000</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6509669</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Färgelanda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Järbo</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-12-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-12-05</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Samuel Sjöberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Samuel Sjöberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33191-2022 artfynd.xlsx
+++ b/artfynd/A 33191-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104306126</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104306813</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -974,6 +989,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104307635</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104929994</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1170,6 +1195,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108668387</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1271,6 +1301,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111826663</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1369,6 +1404,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111826671</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1467,6 +1507,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111827327</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1575,6 +1620,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104930142</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1673,6 +1723,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108668733</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1775,6 +1830,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103382698</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1873,6 +1933,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108668744</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1994,6 +2059,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104929808</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2095,6 +2165,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104929821</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2193,6 +2268,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104945556</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2291,6 +2371,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104945559</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2389,6 +2474,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104928561</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2487,8 +2577,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104945554</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>